--- a/Data/MaKho_MaVV.xlsx
+++ b/Data/MaKho_MaVV.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_BB\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E47E7A-3514-46D9-A8D3-2D78516568E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA0664F-59B3-4D6E-A501-10FCEE95F7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -186,9 +197,6 @@
     <t>HH005QN</t>
   </si>
   <si>
-    <t>Xăng E10 RON95 Mức 3</t>
-  </si>
-  <si>
     <t>HH051-043</t>
   </si>
   <si>
@@ -202,6 +210,9 @@
   </si>
   <si>
     <t>Kho Nghi Sơn</t>
+  </si>
+  <si>
+    <t>Xăng E10 RON 95 Mức 3</t>
   </si>
 </sst>
 </file>
@@ -571,12 +582,12 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -594,12 +605,12 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -620,7 +631,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>32</v>
@@ -662,7 +673,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
